--- a/data/trans_dic/P64D$publico_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,26</t>
+          <t>2,04; 9,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 40,59</t>
+          <t>12,8; 40,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 18,62</t>
+          <t>6,59; 19,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,83</t>
+          <t>3,58; 8,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,37</t>
+          <t>7,61; 12,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,67</t>
+          <t>5,6; 9,57</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,0</t>
+          <t>4,18; 9,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,1</t>
+          <t>6,23; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,35</t>
+          <t>5,78; 9,22</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,94</t>
+          <t>4,21; 8,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,86</t>
+          <t>8,27; 12,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,28</t>
+          <t>6,41; 9,23</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2620; 12234</t>
+          <t>2691; 12271</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10547; 32650</t>
+          <t>10294; 32330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14538; 39572</t>
+          <t>13999; 41845</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51315; 122069</t>
+          <t>49529; 121500</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71971; 116922</t>
+          <t>71880; 118154</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131448; 225102</t>
+          <t>130426; 222651</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18891; 40263</t>
+          <t>18690; 41834</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28325; 48331</t>
+          <t>27118; 48443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52284; 82528</t>
+          <t>51019; 81410</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84786; 155792</t>
+          <t>82649; 157981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118782; 173177</t>
+          <t>120810; 176195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>215480; 317775</t>
+          <t>219318; 315820</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$publico_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,29</t>
+          <t>3,03; 10,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,8; 40,19</t>
+          <t>11,96; 26,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 19,69</t>
+          <t>7,21; 15,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,79</t>
+          <t>7,39; 11,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,5</t>
+          <t>10,28; 14,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,57</t>
+          <t>9,18; 11,91</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,35</t>
+          <t>4,31; 9,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,13</t>
+          <t>6,47; 10,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,22</t>
+          <t>6,07; 9,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,05</t>
+          <t>6,83; 9,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,06</t>
+          <t>10,07; 13,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,23</t>
+          <t>8,67; 10,69</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>26272</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2691; 12271</t>
+          <t>4974; 17843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10294; 32330</t>
+          <t>10525; 23357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13999; 41845</t>
+          <t>18159; 37872</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92455</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94949</t>
+          <t>115558</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187404</t>
+          <t>232037</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49529; 121500</t>
+          <t>93833; 140856</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71880; 118154</t>
+          <t>97220; 136374</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130426; 222651</t>
+          <t>203492; 263852</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36661</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65126</t>
+          <t>71911</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18690; 41834</t>
+          <t>20992; 45910</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27118; 48443</t>
+          <t>30903; 52020</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51019; 81410</t>
+          <t>58607; 90989</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>126992</t>
+          <t>157445</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275635</t>
+          <t>330220</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82649; 157981</t>
+          <t>131243; 186454</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120810; 176195</t>
+          <t>152104; 196813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219318; 315820</t>
+          <t>297716; 367058</t>
         </is>
       </c>
     </row>
